--- a/data/trans_orig/P5B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>692</t>
+          <t>688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5641</t>
+          <t>6299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>653</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5436</t>
+          <t>5307</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1433</t>
+          <t>1372</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8311</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>72918</t>
+          <t>72260</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>77867</t>
+          <t>77871</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,82%</t>
+          <t>91,98%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>83028</t>
+          <t>83157</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>87815</t>
+          <t>87811</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,86%</t>
+          <t>94,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158722</t>
+          <t>158712</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165590</t>
+          <t>165651</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,02%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>99,18%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2522</t>
+          <t>2654</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10704</t>
+          <t>10720</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4388</t>
+          <t>4420</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12739</t>
+          <t>13743</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>7,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8617</t>
+          <t>9062</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21266</t>
+          <t>21189</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176542</t>
+          <t>176526</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184724</t>
+          <t>184592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,58%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>175992</t>
+          <t>174988</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184343</t>
+          <t>184311</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>93,25%</t>
+          <t>92,72%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354711</t>
+          <t>354788</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>367360</t>
+          <t>366915</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,36%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,59%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1862</t>
+          <t>1971</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8476</t>
+          <t>8907</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>9,8%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4021</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2702</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10791</t>
+          <t>10274</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,59%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78003</t>
+          <t>77572</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>84617</t>
+          <t>84508</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>90,2%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>97,85%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>99240</t>
+          <t>99339</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1582,7 +1582,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,11%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>178949</t>
+          <t>179466</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>187038</t>
+          <t>186727</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,31%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,58%</t>
+          <t>98,41%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3377</t>
+          <t>3591</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>12778</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1919</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9150</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>7090</t>
+          <t>6852</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17813</t>
+          <t>17790</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>139199</t>
+          <t>138297</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>147698</t>
+          <t>147484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,14%</t>
+          <t>91,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>138824</t>
+          <t>138944</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>146175</t>
+          <t>146166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,7 +1925,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281356</t>
+          <t>281379</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292079</t>
+          <t>292317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1965,7 +1965,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,71%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12821</t>
+          <t>13613</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26356</t>
+          <t>28203</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10112</t>
+          <t>10573</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>22704</t>
+          <t>23863</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>27284</t>
+          <t>26612</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>46386</t>
+          <t>44725</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>477003</t>
+          <t>475156</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>490538</t>
+          <t>489746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,76%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>97,45%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>505845</t>
+          <t>504686</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>518437</t>
+          <t>517976</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,7%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,09%</t>
+          <t>98,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>985522</t>
+          <t>987183</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1004624</t>
+          <t>1005296</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,36%</t>
+          <t>97,42%</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3428</t>
+          <t>3958</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2700,7 +2700,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2720,7 +2720,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5467</t>
+          <t>5372</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>886</t>
+          <t>674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7151</t>
+          <t>6779</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,16%</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2793,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99959</t>
+          <t>99429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>105828</t>
+          <t>105923</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,09%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>207531</t>
+          <t>207903</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>213796</t>
+          <t>214008</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,67%</t>
+          <t>96,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,59%</t>
+          <t>99,69%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1417</t>
+          <t>1721</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>8572</t>
+          <t>8047</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1544</t>
+          <t>1382</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>8338</t>
+          <t>8674</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>4590</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14219</t>
+          <t>14431</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,09%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>150772</t>
+          <t>151297</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>157927</t>
+          <t>157623</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>184886</t>
+          <t>184550</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>191680</t>
+          <t>191842</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,2%</t>
+          <t>99,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338349</t>
+          <t>338137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>348177</t>
+          <t>347978</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,75%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -3371,7 +3371,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>3978</t>
+          <t>3507</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3386,7 +3386,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3406,7 +3406,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>3246</t>
+          <t>3224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4813</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -3479,7 +3479,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>94002</t>
+          <t>94473</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3494,7 +3494,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,94%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>97845</t>
+          <t>97867</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,79%</t>
+          <t>96,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194258</t>
+          <t>194353</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1414</t>
+          <t>1413</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7471</t>
+          <t>7969</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3729,7 +3729,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>607</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5374</t>
+          <t>5196</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3764,7 +3764,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2623</t>
+          <t>2603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>9886</t>
+          <t>10896</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>4,42%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107546</t>
+          <t>107048</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>113603</t>
+          <t>113604</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,5%</t>
+          <t>93,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>126328</t>
+          <t>126506</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>131101</t>
+          <t>131095</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>236833</t>
+          <t>235823</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244096</t>
+          <t>244116</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,99%</t>
+          <t>95,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,94%</t>
+          <t>98,95%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5359</t>
+          <t>5181</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15093</t>
+          <t>16126</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14371</t>
+          <t>14072</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>11532</t>
+          <t>12034</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26127</t>
+          <t>26919</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,66%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>460636</t>
+          <t>459603</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>470370</t>
+          <t>470548</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>96,83%</t>
+          <t>96,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>522941</t>
+          <t>523240</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>532817</t>
+          <t>532717</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,33%</t>
+          <t>97,38%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>986914</t>
+          <t>986122</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001509</t>
+          <t>1001007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,34%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -4632,7 +4632,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4601</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4647,7 +4647,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4667,7 +4667,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3976</t>
+          <t>3946</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5761</t>
+          <t>5660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>97567</t>
+          <t>97295</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4755,7 +4755,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4775,7 +4775,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94291</t>
+          <t>94321</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -4790,7 +4790,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>95,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194674</t>
+          <t>194775</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4825,7 +4825,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7492</t>
+          <t>7352</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>669</t>
+          <t>648</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>6367</t>
+          <t>6190</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,31%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2940</t>
+          <t>2681</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>10840</t>
+          <t>11387</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,12%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>147514</t>
+          <t>147654</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>153791</t>
+          <t>153457</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>203547</t>
+          <t>203724</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>209245</t>
+          <t>209266</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354079</t>
+          <t>353532</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>361979</t>
+          <t>362238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,03%</t>
+          <t>96,88%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,19%</t>
+          <t>99,27%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1284</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7310</t>
+          <t>8272</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>1947</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9159</t>
+          <t>9299</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5403,7 +5403,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>136358</t>
+          <t>135396</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>142373</t>
+          <t>142384</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,7 +5461,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>127749</t>
+          <t>127910</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -5476,7 +5476,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,65%</t>
+          <t>96,78%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266681</t>
+          <t>266541</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273889</t>
+          <t>273893</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,68%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -5661,7 +5661,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2671</t>
+          <t>4011</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>4741</t>
+          <t>5283</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>614</t>
+          <t>603</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6194</t>
+          <t>6124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -5769,7 +5769,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>119435</t>
+          <t>118095</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -5784,7 +5784,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>96,72%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5804,7 +5804,7 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>125263</t>
+          <t>124721</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
@@ -5819,7 +5819,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,35%</t>
+          <t>95,94%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>245916</t>
+          <t>245986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251496</t>
+          <t>251507</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,54%</t>
+          <t>97,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>5589</t>
+          <t>5434</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>15446</t>
+          <t>15144</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3294</t>
+          <t>3152</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11606</t>
+          <t>11816</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10137</t>
+          <t>9970</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22690</t>
+          <t>22026</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>507503</t>
+          <t>507805</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>517360</t>
+          <t>517515</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>97,1%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,93%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>558749</t>
+          <t>558539</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>567061</t>
+          <t>567203</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,42%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1070614</t>
+          <t>1071278</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1083167</t>
+          <t>1083334</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>592</t>
+          <t>662</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5379</t>
+          <t>5338</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6614,7 +6614,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4077</t>
+          <t>3799</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6629,7 +6629,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1170</t>
+          <t>1283</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6861</t>
+          <t>7169</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>52132</t>
+          <t>52173</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>56919</t>
+          <t>56849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,7 +6722,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57367</t>
+          <t>57645</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -6737,7 +6737,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,36%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>112094</t>
+          <t>111786</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117785</t>
+          <t>117672</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,23%</t>
+          <t>93,97%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>98,92%</t>
         </is>
       </c>
     </row>
@@ -6922,7 +6922,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4322</t>
+          <t>5479</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6937,7 +6937,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1600</t>
+          <t>1498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9990</t>
+          <t>9646</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,82%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2479</t>
+          <t>2705</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11482</t>
+          <t>11857</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,48%</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>154977</t>
+          <t>153820</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -7045,7 +7045,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,29%</t>
+          <t>96,56%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>171866</t>
+          <t>172210</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>180256</t>
+          <t>180358</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,51%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,18%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>329673</t>
+          <t>329298</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338676</t>
+          <t>338450</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4667</t>
+          <t>4745</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,21%</t>
+          <t>2,24%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4530</t>
+          <t>4539</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>206880</t>
+          <t>206802</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>380904</t>
+          <t>380895</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -7608,7 +7608,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99551</t>
+          <t>99907</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7623,7 +7623,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>36,24%</t>
+          <t>36,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1125</t>
+          <t>1152</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>7820</t>
+          <t>7898</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3314</t>
+          <t>2841</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>127422</t>
+          <t>120811</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>20,82%</t>
         </is>
       </c>
     </row>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>175150</t>
+          <t>174794</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -7731,7 +7731,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>297663</t>
+          <t>297585</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>304358</t>
+          <t>304331</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,44%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>452762</t>
+          <t>459373</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>576870</t>
+          <t>577343</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>79,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,43%</t>
+          <t>99,51%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3343</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>110326</t>
+          <t>121356</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5221</t>
+          <t>5599</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17062</t>
+          <t>16017</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12694</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>134992</t>
+          <t>155409</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>10,9%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>555073</t>
+          <t>544043</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>662056</t>
+          <t>662139</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>83,42%</t>
+          <t>81,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>743268</t>
+          <t>744313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>755109</t>
+          <t>754731</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1290737</t>
+          <t>1270320</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413035</t>
+          <t>1413051</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,7 +8144,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>89,1%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">

--- a/data/trans_orig/P5B_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P5B_R-Edad-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -728,67 +728,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>650</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5926</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2,29%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>6,7%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>2110</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>688</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5659</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,69%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,88%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,02%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>653</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5307</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>2,29%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1372</t>
+          <t>1384</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8311</t>
+          <t>8379</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,82%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>5,02%</t>
         </is>
       </c>
     </row>
@@ -836,74 +836,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>86436</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82538</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>87814</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>97,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>93,3%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>76449</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>72260</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>72900</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>77871</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,31%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,98%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>92,8%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>99,12%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>129</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>86436</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>83157</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>87811</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>97,71%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,0%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>99,26%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>245</t>
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158712</t>
+          <t>158644</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>165651</t>
+          <t>165639</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,02%</t>
+          <t>94,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,18%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -949,57 +949,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88464</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>119</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>78559</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>132</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>88464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1066,72 +1066,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>8141</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>4434</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>13742</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4,31%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,35%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>5465</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>10720</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2411</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>10787</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,92%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,42%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>8141</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>4420</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>13743</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>4,31%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,28%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>8525</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>21189</t>
+          <t>20540</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,46%</t>
         </is>
       </c>
     </row>
@@ -1184,67 +1184,67 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
+          <t>180590</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>174989</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>184297</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>95,69%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>92,72%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>97,65%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
           <t>181781</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>176526</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>184592</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>176459</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>184835</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,08%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,58%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>180590</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>174988</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>184311</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>95,69%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>94,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>354788</t>
+          <t>355437</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>366915</t>
+          <t>367452</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>94,36%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,59%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1292,57 +1292,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>188731</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>279</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>187246</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>284</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>188731</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1409,72 +1409,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1172</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4389</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>4636</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1971</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8907</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1995</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>9356</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,36%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,28%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>10,3%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1172</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3922</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,14%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,8%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3013</t>
+          <t>3005</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>10274</t>
+          <t>10298</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,43%</t>
         </is>
       </c>
     </row>
@@ -1522,72 +1522,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>102089</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>98872</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>95,75%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>120</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>81843</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>77572</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>84508</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>77123</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>84484</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>94,64%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>89,7%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>97,72%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>102089</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>99339</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,86%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,2%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>179466</t>
+          <t>179442</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>186727</t>
+          <t>186735</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>94,59%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,42%</t>
         </is>
       </c>
     </row>
@@ -1635,57 +1635,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>103261</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>127</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>86479</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>103261</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1752,72 +1752,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4578</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1967</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8681</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>3,09%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>1,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>10</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>7064</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>3591</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>12778</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>3529</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>12505</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>4,68%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>2,38%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>8,46%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4578</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1928</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9150</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>6852</t>
+          <t>6784</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>17790</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,86%</t>
         </is>
       </c>
     </row>
@@ -1865,72 +1865,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>143516</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>139413</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>146127</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>96,91%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>94,14%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>98,67%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>211</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>144011</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>138297</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>147484</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>138570</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>147546</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>95,32%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>91,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>97,62%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>143516</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>138944</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>146166</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>96,91%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>91,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>281379</t>
+          <t>281631</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>292317</t>
+          <t>292385</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,05%</t>
+          <t>94,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,73%</t>
         </is>
       </c>
     </row>
@@ -1978,57 +1978,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>148094</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>221</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>151075</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>223</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>148094</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2095,72 +2095,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>15919</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>9852</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>23333</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,86%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>19275</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>13613</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>28203</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>13041</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>27491</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>3,83%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>15919</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>10573</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>23863</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>3,01%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>26612</t>
+          <t>26158</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>44725</t>
+          <t>44427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,31%</t>
         </is>
       </c>
     </row>
@@ -2208,72 +2208,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>512630</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>505216</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>518697</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>96,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95,59%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>98,14%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>718</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>484084</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>475156</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>489746</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>475868</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>490318</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>96,17%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>94,4%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>97,3%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>512630</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>504686</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>517976</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>96,99%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>94,54%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,0%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>987183</t>
+          <t>987481</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1005296</t>
+          <t>1005750</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,67%</t>
+          <t>95,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,42%</t>
+          <t>97,47%</t>
         </is>
       </c>
     </row>
@@ -2321,57 +2321,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>792</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>528549</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>746</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>503359</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>792</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>528549</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2491,7 +2491,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2502,7 +2502,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2675,67 +2675,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1557</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>5839</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,4%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,25%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1108</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3958</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>3993</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,07%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1557</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>5372</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,4%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>674</t>
+          <t>668</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6779</t>
+          <t>6933</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2770,7 +2770,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,23%</t>
         </is>
       </c>
     </row>
@@ -2783,74 +2783,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>109738</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>105456</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>111295</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,6%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,75%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>102279</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>99429</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>99394</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>103387</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,93%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>96,17%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>96,14%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>109738</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>105923</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>111295</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,6%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>95,17%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>306</t>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>207903</t>
+          <t>207749</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>214008</t>
+          <t>214014</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,7 +2878,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,84%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2896,57 +2896,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>111295</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>111295</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>111295</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>103387</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>103387</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>103387</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>157</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>111295</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>111295</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>111295</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3018,67 +3018,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>4223</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1594</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>8918</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,19%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,82%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>4,62%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>4218</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1721</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8047</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1827</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>9186</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,65%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4223</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1382</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>8674</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,19%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>4590</t>
+          <t>4245</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>14431</t>
+          <t>13779</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>3,91%</t>
         </is>
       </c>
     </row>
@@ -3126,72 +3126,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>189001</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>184306</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>191630</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,81%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>95,38%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,18%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>225</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>155126</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>151297</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>157623</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>150158</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>157517</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,35%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>94,95%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>262</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>189001</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>184550</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>191842</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,81%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,51%</t>
+          <t>94,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,28%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>338137</t>
+          <t>338789</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>347978</t>
+          <t>348323</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>96,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,8%</t>
         </is>
       </c>
     </row>
@@ -3239,57 +3239,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>193224</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>231</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>159344</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>268</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>193224</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3361,102 +3361,102 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>647</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3233</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,2%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>695</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3507</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>3475</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>3,58%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>647</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>3,55%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1342</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>3224</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,64%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4683</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>3,19%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1342</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4718</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,67%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -3469,74 +3469,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>100444</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>97858</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>101091</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,36%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,8%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>97285</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>94473</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>94505</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,29%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96,42%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>96,45%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>100444</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>97867</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>101091</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,36%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>96,81%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>284</t>
@@ -3549,7 +3549,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>194353</t>
+          <t>194388</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,63%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3582,57 +3582,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>101091</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>101091</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>101091</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>138</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>97980</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>101091</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>101091</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>101091</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3699,72 +3699,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1922</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>606</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5263</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,46%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,46%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,0%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3616</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1413</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7969</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1355</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8133</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>6,93%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1922</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>607</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5196</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,46%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2603</t>
+          <t>2700</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>10896</t>
+          <t>10488</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,25%</t>
         </is>
       </c>
     </row>
@@ -3812,72 +3812,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>129780</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>126439</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>131096</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,54%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>96,0%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,54%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>158</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>111401</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>107048</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>113604</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>106884</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>113662</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>96,86%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>93,07%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>98,77%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>129780</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>126506</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>131095</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,54%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>235823</t>
+          <t>236231</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>244116</t>
+          <t>244019</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,95%</t>
+          <t>98,91%</t>
         </is>
       </c>
     </row>
@@ -3925,57 +3925,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>131702</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>115017</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>115017</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>115017</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>194</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>131702</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4042,72 +4042,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>8349</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4738</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>14816</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>14</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9636</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5181</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>16126</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5602</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>15733</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>2,03%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,09%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>3,39%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>8349</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>4595</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>14072</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12034</t>
+          <t>12306</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26919</t>
+          <t>25324</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -4155,72 +4155,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>755</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>528963</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>522496</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>532574</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,24%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,12%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>671</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>466093</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>459603</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>470548</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>459996</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>470127</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>97,97%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96,61%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,91%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>755</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>528963</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>523240</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>532717</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,38%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,14%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>986122</t>
+          <t>987717</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001007</t>
+          <t>1000735</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,79%</t>
         </is>
       </c>
     </row>
@@ -4268,57 +4268,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>537312</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>685</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>475729</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>475729</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>475729</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>767</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>537312</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4438,7 +4438,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4449,7 +4449,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4617,72 +4617,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>795</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4742</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>4,83%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1610</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>467</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>4873</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4452</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,58%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,77%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>795</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>3946</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>576</t>
+          <t>792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5660</t>
+          <t>6729</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>3,36%</t>
         </is>
       </c>
     </row>
@@ -4730,72 +4730,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>97472</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>93525</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>99,19%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>95,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>161</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>100558</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>97295</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>101701</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>97716</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>101708</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,42%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,23%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>99,54%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>97472</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>94321</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>99,19%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>95,98%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>194775</t>
+          <t>193706</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199859</t>
+          <t>199643</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,18%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,71%</t>
+          <t>99,6%</t>
         </is>
       </c>
     </row>
@@ -4843,57 +4843,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>98267</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>164</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>102168</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>102168</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>102168</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>98267</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4960,72 +4960,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>2654</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>665</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>6796</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1,26%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3625</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1549</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7352</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1262</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>7490</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>2,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,0%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>4,74%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>2654</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>648</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>6190</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>1,26%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2681</t>
+          <t>3013</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11387</t>
+          <t>11293</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -5073,72 +5073,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>207260</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>203118</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>209249</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>98,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96,76%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,68%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>151381</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>147654</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>153457</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>147516</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>153744</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>97,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>95,26%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,0%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>306</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>207260</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>203724</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>209266</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>98,74%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>97,05%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,69%</t>
+          <t>99,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>353532</t>
+          <t>353626</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>362238</t>
+          <t>361906</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,88%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,27%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -5186,57 +5186,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>209914</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>209914</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>209914</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>246</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>155006</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>155006</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>155006</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>310</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>209914</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>209914</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>209914</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5303,72 +5303,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1348</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4326</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,27%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>3464</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1284</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>8272</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>1237</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>8336</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>2,41%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,89%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,76%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1348</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4261</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1947</t>
+          <t>1913</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>9299</t>
+          <t>9523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
     </row>
@@ -5416,72 +5416,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>130823</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>127845</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96,73%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>201</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>140204</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>135396</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>142384</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>135332</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>142431</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>97,59%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>94,24%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>99,11%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>186</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>130823</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>127910</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>98,98%</t>
-        </is>
-      </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>94,2%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>266541</t>
+          <t>266317</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>273893</t>
+          <t>273927</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,29%</t>
+          <t>99,31%</t>
         </is>
       </c>
     </row>
@@ -5529,57 +5529,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>132171</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>206</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>143668</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>143668</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>143668</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>188</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>132171</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5646,72 +5646,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1502</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5744</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,16%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>4,42%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>657</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>4011</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3286</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,54%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1502</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5283</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>603</t>
+          <t>610</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6124</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,5%</t>
         </is>
       </c>
     </row>
@@ -5759,74 +5759,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>128502</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>124260</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>95,58%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>169</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>121449</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>118095</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>118820</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,46%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96,72%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>97,31%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>128502</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>124721</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>95,94%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>343</t>
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>245986</t>
+          <t>245795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>251507</t>
+          <t>251500</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,7 +5854,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5872,57 +5872,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>130004</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>170</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>122106</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>130004</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5989,72 +5989,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6299</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3160</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>12253</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>9356</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>15144</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>5349</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>14758</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>1,79%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>1,04%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>6299</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>3152</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>11816</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>1,1%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,82%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9970</t>
+          <t>9986</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>22026</t>
+          <t>22931</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6089,7 +6089,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -6102,72 +6102,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>564056</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>558102</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>567195</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,9%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,85%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,45%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>771</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>513593</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>507805</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>517515</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>508191</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>517600</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>98,21%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>97,1%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>98,96%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>815</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>564056</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>558539</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>567203</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>98,9%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1071278</t>
+          <t>1070373</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1083334</t>
+          <t>1083318</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,7 +6197,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -6215,57 +6215,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>570355</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>786</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>522949</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
         <is>
           <t>522949</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
         <is>
           <t>522949</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>824</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>570355</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6385,7 +6385,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6396,7 +6396,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6564,72 +6564,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>3003</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,84%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,94%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>2207</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>662</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5338</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>3,84%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>1,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>9,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>1127</t>
+          <t>2210</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>692</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>3799</t>
+          <t>5611</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>3334</t>
+          <t>3139</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1283</t>
+          <t>1189</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>7169</t>
+          <t>6804</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -6677,72 +6677,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>49608</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>47534</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,16%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,06%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>105</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>55304</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>52173</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>56849</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>96,16%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>90,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>98,85%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>60317</t>
+          <t>49880</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>57645</t>
+          <t>46479</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>51398</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>95,76%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,82%</t>
+          <t>89,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>115621</t>
+          <t>99488</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111786</t>
+          <t>95823</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>117672</t>
+          <t>101438</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>96,94%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,84%</t>
         </is>
       </c>
     </row>
@@ -6790,57 +6790,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>50537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>109</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>57511</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>116</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61444</t>
+          <t>52090</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>118955</t>
+          <t>102627</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6907,72 +6907,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4344</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1473</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>10259</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2,77%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,94%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>6,54%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>1441</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>1490</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5479</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,9%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>4768</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>1498</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>9646</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,82%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>5867</t>
+          <t>5833</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>2705</t>
+          <t>2506</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>11857</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,83%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -7020,74 +7020,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>152609</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>146694</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>155480</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>97,23%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>93,46%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,06%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>157858</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>153820</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>99,1%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96,56%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>144028</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>140750</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>96,72%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>270</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>177430</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>172210</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>180358</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>97,57%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>94,7%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,18%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>526</t>
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>335288</t>
+          <t>296638</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>329298</t>
+          <t>291428</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>338450</t>
+          <t>299965</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,21%</t>
+          <t>99,17%</t>
         </is>
       </c>
     </row>
@@ -7133,57 +7133,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>156953</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>156953</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>156953</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>181856</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>181856</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>181856</t>
+          <t>145518</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>341155</t>
+          <t>302471</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341155</t>
+          <t>302471</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>341155</t>
+          <t>302471</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7250,107 +7250,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4741</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,38%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4745</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>4822</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>910</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4539</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,24%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,29%</t>
         </is>
       </c>
     </row>
@@ -7363,74 +7363,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>198216</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>194428</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,52%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,62%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>175518</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>241</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>210637</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>206802</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>211547</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,57%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,76%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -7438,27 +7438,27 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>384524</t>
+          <t>373733</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>380895</t>
+          <t>369864</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,75%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -7476,57 +7476,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>199169</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>173888</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>211547</t>
+          <t>175518</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>385434</t>
+          <t>374686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7593,72 +7593,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>3036</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>998</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7949</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>27634</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>3544</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>99907</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>10,06%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>18969</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1,39%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>36,37%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1152</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7898</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>1,07%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,38%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30912</t>
+          <t>6580</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2841</t>
+          <t>2487</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>120811</t>
+          <t>19036</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>3,47%</t>
         </is>
       </c>
     </row>
@@ -7706,74 +7706,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>289609</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>284696</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>291647</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>98,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>97,28%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,66%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>339</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>247067</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>174794</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>274701</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>89,94%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>63,63%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>252190</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>236765</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>255734</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>98,61%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>92,58%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>337</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>302204</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>297585</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>304331</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>98,93%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>97,41%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,62%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>676</t>
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>549272</t>
+          <t>541799</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>459373</t>
+          <t>529343</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>577343</t>
+          <t>545892</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,67%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,18%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,55%</t>
         </is>
       </c>
     </row>
@@ -7819,57 +7819,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>342</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>292645</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>341</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>274701</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>274701</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>274701</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>342</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255734</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255734</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>255734</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>580184</t>
+          <t>548379</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>580184</t>
+          <t>548379</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>580184</t>
+          <t>548379</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7936,72 +7936,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>9262</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4997</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>15865</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>1,32%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>0,71%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>2,27%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>31282</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3260</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>121356</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,7%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0,49%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>18,24%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>9741</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5599</t>
+          <t>3141</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16017</t>
+          <t>17899</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>41023</t>
+          <t>16506</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>12678</t>
+          <t>9948</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155409</t>
+          <t>27531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>2,07%</t>
         </is>
       </c>
     </row>
@@ -8049,72 +8049,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>690042</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>683439</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>694307</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>98,68%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>97,73%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>99,29%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>934</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>634117</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>544043</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>662139</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>95,3%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>81,76%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>99,51%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>962</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>750589</t>
+          <t>621615</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>744313</t>
+          <t>610960</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>754731</t>
+          <t>625718</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>98,72%</t>
+          <t>98,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>97,89%</t>
+          <t>97,15%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1384706</t>
+          <t>1311657</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1270320</t>
+          <t>1300632</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1413051</t>
+          <t>1318215</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>97,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,25%</t>
         </is>
       </c>
     </row>
@@ -8162,57 +8162,57 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>975</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>699304</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>665399</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>665399</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>665399</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>975</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628859</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628859</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>760330</t>
+          <t>628859</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1425729</t>
+          <t>1328163</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1425729</t>
+          <t>1328163</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1425729</t>
+          <t>1328163</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
